--- a/_01_main/_05_validation/LibMan_renaming_test_names.xlsx
+++ b/_01_main/_05_validation/LibMan_renaming_test_names.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davis\00_data\01_Projects\Personal\SCDL\_01_main\_05_validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB500BC-8111-410D-8F07-499E74184F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760C7A01-12DD-4E39-9A75-97A06C4CE4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="21255" xr2:uid="{9664D8D8-E09F-4482-9132-8996544CFBDA}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21390" xr2:uid="{9664D8D8-E09F-4482-9132-8996544CFBDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="77">
   <si>
     <t>𝐏𝐑𝐄𝐌𝐈𝐄𝐑𝐄| [TFT Records] Illiam Patrol - With My Fist [TFT004]</t>
   </si>
@@ -261,6 +261,12 @@
   </si>
   <si>
     <t>Artist - Title (Some Artist Remix)</t>
+  </si>
+  <si>
+    <t>LOBITA - ØSLO X R2B</t>
+  </si>
+  <si>
+    <t>Lobita - Øslo x R2B</t>
   </si>
 </sst>
 </file>
@@ -372,8 +378,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5182053D-6F20-4172-AF69-D0E0E90DC848}" name="Table1" displayName="Table1" ref="A1:B52" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
-  <autoFilter ref="A1:B52" xr:uid="{5182053D-6F20-4172-AF69-D0E0E90DC848}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5182053D-6F20-4172-AF69-D0E0E90DC848}" name="Table1" displayName="Table1" ref="A1:B53" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+  <autoFilter ref="A1:B53" xr:uid="{5182053D-6F20-4172-AF69-D0E0E90DC848}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{8F0CE10E-8C57-4604-8DCE-B814BB6E48C1}" name="original_filename" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{88DAEAD9-00FD-438D-8E25-BAA0671EA225}" name="correct_filename" dataDxfId="0"/>
@@ -699,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C28437CC-2DD0-43B3-B933-50C4FE5FA466}">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="71.42578125" customWidth="1"/>
@@ -866,16 +872,16 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" t="s">
-        <v>19</v>
+      <c r="A21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
         <v>19</v>
@@ -883,7 +889,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" t="s">
         <v>19</v>
@@ -891,7 +897,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
         <v>19</v>
@@ -899,7 +905,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
         <v>19</v>
@@ -907,39 +913,39 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B30" t="s">
         <v>19</v>
@@ -947,7 +953,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B31" t="s">
         <v>19</v>
@@ -955,15 +961,15 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B33" t="s">
         <v>24</v>
@@ -971,153 +977,161 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B35" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>27</v>
+      </c>
+      <c r="B36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>28</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>58</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+      <c r="B39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>60</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+      <c r="B40" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>61</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
+      <c r="B41" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>62</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
+      <c r="B42" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>63</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+      <c r="B43" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>64</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
+      <c r="B44" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>65</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>66</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+      <c r="B46" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>72</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B47" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>73</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B48" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>68</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
+      <c r="B49" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>67</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+      <c r="B50" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>69</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
+      <c r="B51" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>71</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
+      <c r="B52" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>70</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B53" t="s">
         <v>19</v>
       </c>
     </row>
